--- a/data/2026/02/서비스 리드타임 현황.xlsx
+++ b/data/2026/02/서비스 리드타임 현황.xlsx
@@ -675,36 +675,36 @@
         </is>
       </c>
       <c r="G2" s="14" t="n">
-        <v>1473.0</v>
+        <v>1105.0</v>
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>241.75</t>
+          <t>252.39</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
         <is>
-          <t>196.36</t>
+          <t>203.88</t>
         </is>
       </c>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K2" s="14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="L2" s="14" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="M2" s="14" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>40.68</t>
         </is>
       </c>
       <c r="N2" s="14" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>37.90</t>
         </is>
       </c>
     </row>
@@ -746,21 +746,21 @@
         </is>
       </c>
       <c r="G3" s="14" t="n">
-        <v>564.0</v>
+        <v>473.0</v>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>130.15</t>
+          <t>119.19</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
-          <t>117.28</t>
+          <t>106.81</t>
         </is>
       </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="K3" s="14" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="M3" s="14" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="N3" s="14" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>23.45</t>
         </is>
       </c>
     </row>
@@ -817,46 +817,46 @@
         </is>
       </c>
       <c r="G4" s="14" t="n">
-        <v>102.0</v>
+        <v>74.0</v>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>268.61</t>
+          <t>308.78</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>251.82</t>
+          <t>250.97</t>
         </is>
       </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="K4" s="14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="L4" s="14" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>12.83</t>
         </is>
       </c>
       <c r="M4" s="14" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>43.98</t>
         </is>
       </c>
       <c r="N4" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>51.68</t>
         </is>
       </c>
     </row>
@@ -888,36 +888,36 @@
         </is>
       </c>
       <c r="G5" s="14" t="n">
-        <v>28.0</v>
+        <v>19.0</v>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>320.23</t>
+          <t>244.63</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>255.74</t>
+          <t>199.40</t>
         </is>
       </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>10.13</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="M5" s="14" t="inlineStr">
         <is>
-          <t>54.27</t>
+          <t>42.17</t>
         </is>
       </c>
       <c r="N5" s="14" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>83.33</t>
         </is>
       </c>
     </row>
@@ -959,21 +959,21 @@
         </is>
       </c>
       <c r="G6" s="14" t="n">
-        <v>286.0</v>
+        <v>140.0</v>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>314.59</t>
+          <t>598.15</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>308.57</t>
+          <t>591.42</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="K6" s="14" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.11</t>
         </is>
       </c>
     </row>
@@ -1030,36 +1030,36 @@
         </is>
       </c>
       <c r="G7" s="14" t="n">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>1055.03</t>
+          <t>799.93</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
-          <t>1024.63</t>
+          <t>778.99</t>
         </is>
       </c>
       <c r="J7" s="14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>14.85</t>
         </is>
       </c>
       <c r="N7" s="14" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>27.55</t>
         </is>
       </c>
     </row>
@@ -1101,41 +1101,41 @@
         </is>
       </c>
       <c r="G8" s="14" t="n">
-        <v>161.0</v>
+        <v>155.0</v>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>299.95</t>
+          <t>308.02</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>223.86</t>
+          <t>229.10</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>64.85</t>
         </is>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
@@ -1172,16 +1172,16 @@
         </is>
       </c>
       <c r="G9" s="14" t="n">
-        <v>170.0</v>
+        <v>154.0</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>178.67</t>
+          <t>168.51</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>13.30</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
@@ -1191,27 +1191,27 @@
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>15.07</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
         <is>
-          <t>149.03</t>
+          <t>144.84</t>
         </is>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>78.49</t>
+          <t>146.67</t>
         </is>
       </c>
     </row>
@@ -1243,36 +1243,36 @@
         </is>
       </c>
       <c r="G10" s="14" t="n">
-        <v>139.0</v>
+        <v>74.0</v>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>384.38</t>
+          <t>334.87</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>288.70</t>
+          <t>270.61</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>12.97</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="N10" s="14" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>6.57</t>
         </is>
       </c>
     </row>
@@ -1314,21 +1314,21 @@
         </is>
       </c>
       <c r="G11" s="14" t="n">
-        <v>489.0</v>
+        <v>314.0</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>284.65</t>
+          <t>277.60</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>249.24</t>
+          <t>232.50</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>10.42</t>
         </is>
       </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>13.29</t>
         </is>
       </c>
     </row>
@@ -1385,46 +1385,46 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>255.0</v>
+        <v>185.0</v>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>145.24</t>
+          <t>142.51</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>118.45</t>
+          <t>118.86</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="N12" s="14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>14.87</t>
         </is>
       </c>
     </row>
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="G13" s="14" t="n">
-        <v>49.0</v>
+        <v>38.0</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>306.78</t>
+          <t>309.06</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>230.60</t>
+          <t>244.55</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>24.28</t>
         </is>
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>40.15</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>5.16</t>
         </is>
       </c>
     </row>
@@ -1527,16 +1527,16 @@
         </is>
       </c>
       <c r="G14" s="14" t="n">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>273.90</t>
+          <t>324.81</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>207.63</t>
+          <t>206.34</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
@@ -1546,27 +1546,27 @@
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>95.50</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
     </row>
@@ -1598,21 +1598,21 @@
         </is>
       </c>
       <c r="G15" s="14" t="n">
-        <v>97.0</v>
+        <v>37.0</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>656.54</t>
+          <t>789.38</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>633.07</t>
+          <t>766.12</t>
         </is>
       </c>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
@@ -1622,22 +1622,22 @@
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="M15" s="14" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>12.86</t>
+          <t>15.13</t>
         </is>
       </c>
     </row>
@@ -1669,16 +1669,16 @@
         </is>
       </c>
       <c r="G16" s="14" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>482.16</t>
+          <t>600.76</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>479.74</t>
+          <t>503.71</t>
         </is>
       </c>
       <c r="J16" s="14" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>95.04</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
@@ -1740,21 +1740,21 @@
         </is>
       </c>
       <c r="G17" s="14" t="n">
-        <v>36.0</v>
+        <v>23.0</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>213.48</t>
+          <t>369.57</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>162.73</t>
+          <t>215.41</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
@@ -1764,22 +1764,22 @@
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>11.82</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="M17" s="14" t="inlineStr">
         <is>
-          <t>38.76</t>
+          <t>118.58</t>
         </is>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>18.88</t>
         </is>
       </c>
     </row>
@@ -1811,46 +1811,46 @@
         </is>
       </c>
       <c r="G18" s="14" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>233.31</t>
+          <t>505.14</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>172.43</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>487.02</t>
         </is>
       </c>
       <c r="N18" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1882,16 +1882,16 @@
         </is>
       </c>
       <c r="G19" s="14" t="n">
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>319.40</t>
+          <t>285.08</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>273.86</t>
+          <t>238.33</t>
         </is>
       </c>
       <c r="J19" s="14" t="inlineStr">
@@ -1901,27 +1901,27 @@
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="M19" s="14" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>16.54</t>
         </is>
       </c>
     </row>
@@ -1953,46 +1953,46 @@
         </is>
       </c>
       <c r="G20" s="14" t="n">
-        <v>544.0</v>
+        <v>354.0</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>182.96</t>
+          <t>162.72</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>167.29</t>
+          <t>140.20</t>
         </is>
       </c>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>16.61</t>
         </is>
       </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>14.66</t>
         </is>
       </c>
     </row>
@@ -2024,46 +2024,46 @@
         </is>
       </c>
       <c r="G21" s="14" t="n">
-        <v>305.0</v>
+        <v>241.0</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>98.62</t>
+          <t>119.33</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>101.35</t>
         </is>
       </c>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>10.62</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>5.10</t>
         </is>
       </c>
     </row>
@@ -2095,46 +2095,46 @@
         </is>
       </c>
       <c r="G22" s="14" t="n">
-        <v>30.0</v>
+        <v>26.0</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>180.05</t>
+          <t>305.20</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>149.17</t>
+          <t>285.05</t>
         </is>
       </c>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>18.51</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>8.81</t>
         </is>
       </c>
     </row>
@@ -2166,46 +2166,46 @@
         </is>
       </c>
       <c r="G23" s="14" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>251.33</t>
+          <t>125.62</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>245.85</t>
+          <t>86.87</t>
         </is>
       </c>
       <c r="J23" s="14" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="inlineStr">
+        <is>
+          <t>9.03</t>
+        </is>
+      </c>
+      <c r="M23" s="14" t="inlineStr">
+        <is>
+          <t>29.67</t>
+        </is>
+      </c>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="L23" s="14" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="M23" s="14" t="inlineStr">
-        <is>
-          <t>3.11</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>7.17</t>
         </is>
       </c>
     </row>
@@ -2237,46 +2237,46 @@
         </is>
       </c>
       <c r="G24" s="14" t="n">
-        <v>138.0</v>
+        <v>22.0</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>385.50</t>
+          <t>552.91</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>376.12</t>
+          <t>547.72</t>
         </is>
       </c>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -2308,46 +2308,46 @@
         </is>
       </c>
       <c r="G25" s="14" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>112.85</t>
+          <t>190.87</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>177.15</t>
         </is>
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>12.82</t>
         </is>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>17.47</t>
         </is>
       </c>
     </row>
@@ -2379,16 +2379,16 @@
         </is>
       </c>
       <c r="G26" s="14" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>187.11</t>
+          <t>126.86</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>126.21</t>
+          <t>76.40</t>
         </is>
       </c>
       <c r="J26" s="14" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>43.63</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>57.17</t>
         </is>
       </c>
     </row>
@@ -2450,46 +2450,46 @@
         </is>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>101.01</t>
+          <t>278.04</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
+          <t>75.08</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="J27" s="14" t="inlineStr">
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="M27" s="14" t="inlineStr">
+        <is>
+          <t>200.61</t>
+        </is>
+      </c>
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="M27" s="14" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>816.52</t>
+          <t>206.97</t>
         </is>
       </c>
     </row>
@@ -2521,21 +2521,21 @@
         </is>
       </c>
       <c r="G28" s="14" t="n">
-        <v>23.0</v>
+        <v>19.0</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>116.62</t>
+          <t>80.01</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>111.11</t>
+          <t>62.46</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
@@ -2545,22 +2545,22 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>16.11</t>
         </is>
       </c>
       <c r="N28" s="14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>37.27</t>
+          <t>47.53</t>
         </is>
       </c>
     </row>
@@ -2592,46 +2592,46 @@
         </is>
       </c>
       <c r="G29" s="14" t="n">
-        <v>1872.0</v>
+        <v>1524.0</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>305.19</t>
+          <t>292.44</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>252.59</t>
+          <t>241.53</t>
         </is>
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>13.97</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>31.60</t>
+          <t>33.43</t>
         </is>
       </c>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.29</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2663,46 @@
         </is>
       </c>
       <c r="G30" s="14" t="n">
-        <v>811.0</v>
+        <v>676.0</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>135.72</t>
+          <t>121.65</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>124.10</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>7.84</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="M30" s="14" t="inlineStr">
-        <is>
-          <t>8.21</t>
-        </is>
-      </c>
-      <c r="N30" s="14" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>7.80</t>
         </is>
       </c>
     </row>
@@ -2734,36 +2734,36 @@
         </is>
       </c>
       <c r="G31" s="14" t="n">
-        <v>239.0</v>
+        <v>190.0</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>294.76</t>
+          <t>294.87</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>230.54</t>
+          <t>241.01</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>25.79</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="N31" s="14" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="O31" s="14" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>16.91</t>
         </is>
       </c>
     </row>
@@ -2805,46 +2805,46 @@
         </is>
       </c>
       <c r="G32" s="14" t="n">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>410.46</t>
+          <t>471.45</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>316.85</t>
+          <t>109.85</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>26.10</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>335.44</t>
         </is>
       </c>
       <c r="N32" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>12.99</t>
+          <t>3.83</t>
         </is>
       </c>
     </row>
@@ -2876,36 +2876,36 @@
         </is>
       </c>
       <c r="G33" s="14" t="n">
-        <v>283.0</v>
+        <v>174.0</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>710.81</t>
+          <t>741.81</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>692.40</t>
+          <t>712.43</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="N33" s="14" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>38.29</t>
         </is>
       </c>
     </row>
@@ -2947,46 +2947,46 @@
         </is>
       </c>
       <c r="G34" s="14" t="n">
-        <v>44.0</v>
+        <v>35.0</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>1172.76</t>
+          <t>1090.32</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>1083.93</t>
+          <t>1027.04</t>
         </is>
       </c>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>66.88</t>
+          <t>55.51</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>5.36</t>
         </is>
       </c>
     </row>
@@ -3018,46 +3018,46 @@
         </is>
       </c>
       <c r="G35" s="14" t="n">
-        <v>158.0</v>
+        <v>157.0</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>361.47</t>
+          <t>375.22</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>223.63</t>
+          <t>294.08</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>97.07</t>
+          <t>65.11</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>11.22</t>
+          <t>10.70</t>
         </is>
       </c>
     </row>
@@ -3089,46 +3089,46 @@
         </is>
       </c>
       <c r="G36" s="14" t="n">
-        <v>234.0</v>
+        <v>198.0</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>175.94</t>
+          <t>185.46</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>70.13</t>
+          <t>68.05</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>73.54</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>57.33</t>
+          <t>41.52</t>
         </is>
       </c>
     </row>
@@ -3160,36 +3160,36 @@
         </is>
       </c>
       <c r="G37" s="14" t="n">
-        <v>91.0</v>
+        <v>87.0</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>382.78</t>
+          <t>474.23</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>302.42</t>
+          <t>402.54</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
         <is>
-          <t>61.94</t>
+          <t>61.96</t>
         </is>
       </c>
       <c r="N37" s="14" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>12.50</t>
         </is>
       </c>
     </row>
@@ -3231,21 +3231,21 @@
         </is>
       </c>
       <c r="G38" s="14" t="n">
-        <v>428.0</v>
+        <v>305.0</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>298.75</t>
+          <t>235.76</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>283.99</t>
+          <t>221.94</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
@@ -3255,22 +3255,22 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>10.72</t>
         </is>
       </c>
       <c r="N38" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>20.58</t>
         </is>
       </c>
     </row>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="G39" s="14" t="n">
-        <v>200.0</v>
+        <v>173.0</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>112.34</t>
+          <t>115.88</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>103.62</t>
+          <t>109.57</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>26.12</t>
         </is>
       </c>
     </row>
@@ -3373,16 +3373,16 @@
         </is>
       </c>
       <c r="G40" s="14" t="n">
-        <v>28.0</v>
+        <v>40.0</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>225.90</t>
+          <t>214.48</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>187.86</t>
+          <t>196.34</t>
         </is>
       </c>
       <c r="J40" s="14" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>15.60</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>7.47</t>
         </is>
       </c>
     </row>
@@ -3444,16 +3444,16 @@
         </is>
       </c>
       <c r="G41" s="14" t="n">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>437.89</t>
+          <t>275.70</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>415.08</t>
+          <t>245.21</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -3463,27 +3463,27 @@
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
         <is>
-          <t>15.64</t>
+          <t>24.26</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>7.55</t>
         </is>
       </c>
     </row>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="G42" s="14" t="n">
-        <v>98.0</v>
+        <v>18.0</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>598.94</t>
+          <t>1078.43</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>592.76</t>
+          <t>1074.23</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
@@ -3534,27 +3534,27 @@
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="N42" s="14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>16.41</t>
+          <t>18.79</t>
         </is>
       </c>
     </row>
@@ -3586,16 +3586,16 @@
         </is>
       </c>
       <c r="G43" s="14" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>1252.48</t>
+          <t>1275.52</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>1245.37</t>
+          <t>1116.08</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
@@ -3605,17 +3605,17 @@
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>155.71</t>
         </is>
       </c>
       <c r="N43" s="14" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>15.38</t>
         </is>
       </c>
     </row>
@@ -3657,16 +3657,16 @@
         </is>
       </c>
       <c r="G44" s="14" t="n">
-        <v>21.0</v>
+        <v>27.0</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>315.48</t>
+          <t>322.13</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>213.81</t>
+          <t>284.94</t>
         </is>
       </c>
       <c r="J44" s="14" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>20.07</t>
         </is>
       </c>
     </row>
@@ -3724,50 +3724,121 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>사고수리</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>104.72</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>71.33</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L45" s="14" t="inlineStr">
+        <is>
+          <t>27.35</t>
+        </is>
+      </c>
+      <c r="M45" s="14" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="O45" s="14" t="inlineStr">
+        <is>
+          <t>17.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>내쇼날 모터스</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AS_군산</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Mechanic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>입고 Proactive-RITA</t>
         </is>
       </c>
-      <c r="G45" s="14" t="n">
-        <v>66.0</v>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>362.50</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
-        <is>
-          <t>355.11</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="K45" s="14" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="L45" s="14" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="M45" s="14" t="inlineStr">
-        <is>
-          <t>5.71</t>
-        </is>
-      </c>
-      <c r="N45" s="14" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="O45" s="14" t="inlineStr">
-        <is>
-          <t>28.13</t>
+      <c r="G46" s="14" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>302.61</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>286.28</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>6.91</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
+          <t>9.32</t>
+        </is>
+      </c>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O46" s="14" t="inlineStr">
+        <is>
+          <t>14.19</t>
         </is>
       </c>
     </row>
